--- a/data/trans_dic/IP19C08-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C08-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por selladores, aplicación de flúor</t>
+          <t>Menores que en su última visita al dentista fue por selladores, aplicación de flúor (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,52 +717,52 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 10,93</t>
+          <t>1,16; 10,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 16,24</t>
+          <t>2,91; 16,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,03</t>
+          <t>0,0; 7,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,1</t>
+          <t>0,0; 8,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,76; 14,77</t>
+          <t>1,78; 14,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,12</t>
+          <t>0,0; 7,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 11,31</t>
+          <t>2,09; 11,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 7,22</t>
+          <t>1,28; 7,48</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 13,17</t>
+          <t>3,28; 11,97</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 8,45</t>
+          <t>1,74; 7,94</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 14,12</t>
+          <t>1,53; 13,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,31</t>
+          <t>0,0; 9,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 12,45</t>
+          <t>1,18; 12,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 9,6</t>
+          <t>0,95; 9,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 15,29</t>
+          <t>1,77; 16,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 10,05</t>
+          <t>1,24; 9,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,89</t>
+          <t>0,0; 6,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,78</t>
+          <t>0,0; 6,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 11,63</t>
+          <t>2,61; 11,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 7,17</t>
+          <t>1,3; 7,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,62</t>
+          <t>0,99; 6,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,15</t>
+          <t>0,86; 4,98</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,89</t>
+          <t>0,0; 8,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 15,12</t>
+          <t>1,64; 14,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,2</t>
+          <t>0,0; 9,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 11,75</t>
+          <t>1,51; 12,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,15</t>
+          <t>0,0; 8,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,27</t>
+          <t>0,0; 12,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,48</t>
+          <t>0,0; 13,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 8,48</t>
+          <t>1,38; 8,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 9,16</t>
+          <t>1,61; 8,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,4</t>
+          <t>0,0; 7,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 9,11</t>
+          <t>1,06; 9,49</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 11,63</t>
+          <t>3,76; 11,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,52</t>
+          <t>0,7; 7,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 10,66</t>
+          <t>2,88; 10,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,91</t>
+          <t>0,69; 6,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,42</t>
+          <t>0,63; 6,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 9,44</t>
+          <t>1,53; 9,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 9,8</t>
+          <t>2,6; 10,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 19,46</t>
+          <t>1,49; 18,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 7,8</t>
+          <t>2,93; 7,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 6,04</t>
+          <t>1,74; 6,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 8,6</t>
+          <t>3,42; 9,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 11,4</t>
+          <t>1,58; 12,16</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,96; 16,92</t>
+          <t>4,31; 18,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 8,09</t>
+          <t>0,85; 8,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 10,89</t>
+          <t>1,77; 10,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,75</t>
+          <t>0,0; 6,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 11,07</t>
+          <t>1,15; 10,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 10,33</t>
+          <t>1,86; 10,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,35</t>
+          <t>0,0; 4,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,52</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 10,82</t>
+          <t>3,39; 11,17</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,57</t>
+          <t>2,16; 7,93</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 6,43</t>
+          <t>1,2; 6,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,46</t>
+          <t>0,41; 3,55</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,64; 12,7</t>
+          <t>1,65; 13,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,72</t>
+          <t>0,0; 16,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,56</t>
+          <t>0,0; 13,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,5; 22,78</t>
+          <t>5,31; 22,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,46</t>
+          <t>0,0; 8,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,38</t>
+          <t>0,0; 11,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,14</t>
+          <t>0,0; 7,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,28; 15,34</t>
+          <t>3,61; 14,45</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,31</t>
+          <t>0,0; 7,61</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,9; 7,85</t>
+          <t>0,9; 7,92</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,67</t>
+          <t>0,0; 3,78</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,02; 8,48</t>
+          <t>4,02; 8,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,21</t>
+          <t>2,56; 6,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,34; 6,03</t>
+          <t>2,37; 5,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,9</t>
+          <t>1,19; 3,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,81</t>
+          <t>3,23; 6,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,05</t>
+          <t>2,4; 5,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,34</t>
+          <t>1,55; 4,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 6,43</t>
+          <t>1,86; 6,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,12</t>
+          <t>3,91; 6,84</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,98; 5,42</t>
+          <t>2,94; 5,41</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,49</t>
+          <t>2,35; 4,68</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,65</t>
+          <t>1,93; 4,71</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por selladores, aplicación de flúor (tasa de respuesta: 99,44%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2218</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3778</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1746</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2244</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>5147</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3581</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6021</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>6893</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>633; 5650</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1405; 8146</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5477</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4211</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>728; 5903</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4020</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2006; 11078</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1337; 7791</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2925; 10668</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3581</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2914; 13333</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2187</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1269</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2440</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2477</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>804</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4664</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>3278</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3016</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3117</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>619; 5617</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4529</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>660; 6831</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>596; 5853</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>654; 5947</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>660; 5285</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3546</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4691</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2027; 8835</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>1304; 7249</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1088; 7444</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1153; 6681</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>533</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2730</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2714</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1507</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3248</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3364</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2226</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2935</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>685; 6208</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2766</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>804; 6511</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3216</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4233</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4730</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1222; 7168</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1314; 7183</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5076</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>683; 6091</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6923</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2283</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6103</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2433</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2549</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4227</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5695</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7253</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>9472</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>11798</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>9687</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3687; 11435</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>634; 6440</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3201; 11326</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>767; 7335</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>603; 5868</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1494; 9013</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2675; 10737</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1892; 23168</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>5701; 14880</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>3294; 12327</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>7331; 19416</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3772; 28983</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>5177</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2653</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3464</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1458</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2916</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>4052</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>8093</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>6704</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>4142</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2459</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2353; 9953</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>703; 6784</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1222; 7451</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4738</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>804; 7324</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1371; 8051</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3515</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3893</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>4229; 13925</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3368; 12360</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>1714; 8711</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>709; 6097</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2068</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>6170</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1877</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>661; 5553</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4259</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4350</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1897; 8172</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3141</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3665</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3321</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>2731; 10943</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4809</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>582; 5129</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3368</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>19106</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>13460</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>13233</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>8668</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>16121</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>13790</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>9713</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>16369</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>35227</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>27250</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>22945</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>25037</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>12997; 27292</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>8621; 20643</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>8129; 20401</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>4611; 14642</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>11050; 23512</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>8242; 20343</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>5385; 15528</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>8908; 31810</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>25998; 45450</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>19975; 36736</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>16192; 32286</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>16694; 40731</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C08-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C08-Clase-trans_dic.xlsx
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 10,31</t>
+          <t>1,15; 11,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 16,89</t>
+          <t>2,84; 16,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,47 +732,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,63</t>
+          <t>0,0; 7,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,53</t>
+          <t>0,0; 9,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 14,44</t>
+          <t>1,77; 13,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,96</t>
+          <t>0,0; 11,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 11,53</t>
+          <t>2,45; 12,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 7,48</t>
+          <t>1,31; 7,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,28; 11,97</t>
+          <t>3,16; 12,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,83</t>
+          <t>0,0; 4,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 7,94</t>
+          <t>1,7; 8,03</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 13,87</t>
+          <t>1,53; 14,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,54</t>
+          <t>0,0; 9,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 12,26</t>
+          <t>1,18; 11,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 9,33</t>
+          <t>1,0; 8,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 16,05</t>
+          <t>1,71; 16,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 9,96</t>
+          <t>1,24; 10,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,56</t>
+          <t>0,0; 5,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,55</t>
+          <t>0,0; 5,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 11,39</t>
+          <t>2,74; 12,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,21</t>
+          <t>0,67; 7,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 6,78</t>
+          <t>0,62; 7,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,98</t>
+          <t>0,89; 5,4</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,38</t>
+          <t>0,0; 7,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 14,88</t>
+          <t>1,63; 15,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,9</t>
+          <t>0,0; 9,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 12,2</t>
+          <t>1,28; 11,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,08</t>
+          <t>0,0; 8,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,34</t>
+          <t>0,0; 12,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,04</t>
+          <t>0,0; 13,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 8,11</t>
+          <t>1,32; 8,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 8,81</t>
+          <t>1,61; 9,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,76</t>
+          <t>0,0; 6,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 9,49</t>
+          <t>1,05; 8,76</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 11,65</t>
+          <t>3,86; 11,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 7,06</t>
+          <t>0,69; 7,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 10,19</t>
+          <t>2,67; 9,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,61</t>
+          <t>0,71; 6,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,1</t>
+          <t>0,66; 6,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 9,2</t>
+          <t>1,51; 8,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 10,42</t>
+          <t>2,6; 10,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 18,19</t>
+          <t>1,42; 18,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 7,66</t>
+          <t>2,93; 7,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,52</t>
+          <t>1,81; 6,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 9,07</t>
+          <t>3,51; 8,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 12,16</t>
+          <t>1,58; 10,14</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,31; 18,21</t>
+          <t>4,19; 18,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 8,25</t>
+          <t>0,86; 7,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 10,77</t>
+          <t>1,5; 10,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,92</t>
+          <t>0,0; 7,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 10,46</t>
+          <t>1,15; 10,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 10,93</t>
+          <t>1,9; 11,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,78</t>
+          <t>0,0; 4,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,77</t>
+          <t>0,0; 3,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,39; 11,17</t>
+          <t>3,71; 11,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 7,93</t>
+          <t>2,2; 7,56</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 6,1</t>
+          <t>1,13; 6,14</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,55</t>
+          <t>0,39; 3,47</t>
         </is>
       </c>
     </row>
@@ -1417,17 +1417,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,65; 13,88</t>
+          <t>1,65; 13,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,58</t>
+          <t>0,0; 14,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,34</t>
+          <t>0,0; 13,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,31; 22,87</t>
+          <t>4,05; 22,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,37</t>
+          <t>0,0; 9,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,39</t>
+          <t>0,0; 10,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,53</t>
+          <t>0,0; 9,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,61; 14,45</t>
+          <t>3,69; 13,85</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,61</t>
+          <t>0,0; 7,77</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,9; 7,92</t>
+          <t>0,9; 7,8</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,78</t>
+          <t>0,0; 3,66</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,02; 8,45</t>
+          <t>3,95; 8,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 6,13</t>
+          <t>2,52; 5,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,95</t>
+          <t>2,32; 5,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,79</t>
+          <t>1,21; 3,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,88</t>
+          <t>3,19; 6,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,93</t>
+          <t>2,56; 5,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,47</t>
+          <t>1,42; 4,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 6,65</t>
+          <t>1,89; 6,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,91; 6,84</t>
+          <t>3,97; 6,84</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,41</t>
+          <t>2,78; 5,37</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,68</t>
+          <t>2,33; 4,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,71</t>
+          <t>1,9; 4,77</t>
         </is>
       </c>
     </row>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>633; 5650</t>
+          <t>629; 6466</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1405; 8146</t>
+          <t>1370; 8054</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1942,47 +1942,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5477</t>
+          <t>0; 5542</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4211</t>
+          <t>0; 4816</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>728; 5903</t>
+          <t>722; 5471</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4020</t>
+          <t>0; 5934</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2006; 11078</t>
+          <t>2356; 11787</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1337; 7791</t>
+          <t>1366; 7995</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2925; 10668</t>
+          <t>2817; 10824</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 3581</t>
+          <t>0; 4061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2914; 13333</t>
+          <t>2856; 13473</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>619; 5617</t>
+          <t>618; 5827</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4529</t>
+          <t>0; 4477</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>660; 6831</t>
+          <t>657; 6635</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>596; 5853</t>
+          <t>624; 5381</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>654; 5947</t>
+          <t>632; 6261</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>660; 5285</t>
+          <t>659; 5380</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3546</t>
+          <t>0; 2962</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4691</t>
+          <t>0; 3715</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2027; 8835</t>
+          <t>2122; 9428</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1304; 7249</t>
+          <t>671; 7203</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1088; 7444</t>
+          <t>682; 8140</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1153; 6681</t>
+          <t>1191; 7249</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2935</t>
+          <t>0; 2773</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>685; 6208</t>
+          <t>682; 6326</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2358,47 +2358,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2766</t>
+          <t>0; 2567</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>804; 6511</t>
+          <t>682; 6056</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3216</t>
+          <t>0; 3276</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4233</t>
+          <t>0; 4174</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4730</t>
+          <t>0; 4830</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1222; 7168</t>
+          <t>1168; 7796</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1314; 7183</t>
+          <t>1316; 7459</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 5076</t>
+          <t>0; 4345</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>683; 6091</t>
+          <t>676; 5620</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3687; 11435</t>
+          <t>3785; 11389</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>634; 6440</t>
+          <t>627; 6706</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3201; 11326</t>
+          <t>2971; 10853</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>767; 7335</t>
+          <t>788; 7138</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>603; 5868</t>
+          <t>636; 5916</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1494; 9013</t>
+          <t>1477; 8761</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2675; 10737</t>
+          <t>2678; 10575</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1892; 23168</t>
+          <t>1814; 23695</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5701; 14880</t>
+          <t>5690; 14928</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3294; 12327</t>
+          <t>3431; 12214</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7331; 19416</t>
+          <t>7518; 18855</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3772; 28983</t>
+          <t>3760; 24187</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2353; 9953</t>
+          <t>2289; 10041</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>703; 6784</t>
+          <t>707; 6219</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1222; 7451</t>
+          <t>1036; 7292</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4738</t>
+          <t>0; 5215</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>804; 7324</t>
+          <t>808; 7388</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1371; 8051</t>
+          <t>1400; 8264</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3515</t>
+          <t>0; 3366</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3893</t>
+          <t>0; 3590</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4229; 13925</t>
+          <t>4630; 14029</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3368; 12360</t>
+          <t>3431; 11782</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1714; 8711</t>
+          <t>1615; 8758</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>709; 6097</t>
+          <t>665; 5964</t>
         </is>
       </c>
     </row>
@@ -2967,17 +2967,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>661; 5553</t>
+          <t>661; 5590</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4259</t>
+          <t>0; 3718</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4350</t>
+          <t>0; 4249</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1897; 8172</t>
+          <t>1447; 8049</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3141</t>
+          <t>0; 3531</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3665</t>
+          <t>0; 3291</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3321</t>
+          <t>0; 4250</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2731; 10943</t>
+          <t>2796; 10485</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4809</t>
+          <t>0; 4909</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>582; 5129</t>
+          <t>586; 5055</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 3368</t>
+          <t>0; 3261</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12997; 27292</t>
+          <t>12772; 27283</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8621; 20643</t>
+          <t>8483; 19770</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8129; 20401</t>
+          <t>7967; 20068</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4611; 14642</t>
+          <t>4663; 14854</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11050; 23512</t>
+          <t>10913; 23315</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8242; 20343</t>
+          <t>8791; 20349</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5385; 15528</t>
+          <t>4934; 15427</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8908; 31810</t>
+          <t>9043; 32267</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>25998; 45450</t>
+          <t>26408; 45472</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19975; 36736</t>
+          <t>18876; 36497</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16192; 32286</t>
+          <t>16062; 30873</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>16694; 40731</t>
+          <t>16414; 41248</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C08-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C08-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5,49%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4,05%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7,83%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 11,8</t>
+          <t>0,0; 10,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 16,7</t>
+          <t>1,76; 14,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 7,12</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1,82; 10,85</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,15; 10,93</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2,85; 16,24</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,72</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,76</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,77; 13,38</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,75</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 12,27</t>
+          <t>0,0; 8,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 7,68</t>
+          <t>1,32; 7,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 12,14</t>
+          <t>3,17; 13,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,34</t>
+          <t>0,0; 3,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 8,03</t>
+          <t>1,85; 8,31</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,69%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>5,4%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,67%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>4,38%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,69%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 14,39</t>
+          <t>1,69; 15,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,43</t>
+          <t>1,24; 10,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 11,9</t>
+          <t>0,0; 5,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,58</t>
+          <t>0,0; 5,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 16,9</t>
+          <t>1,52; 14,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 10,14</t>
+          <t>0,0; 8,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,48</t>
+          <t>1,21; 12,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,19</t>
+          <t>0,98; 9,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 12,16</t>
+          <t>2,56; 11,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 7,16</t>
+          <t>1,26; 7,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 7,42</t>
+          <t>0,63; 6,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,4</t>
+          <t>0,74; 4,86</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6,54%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,92</t>
+          <t>1,19; 11,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 15,16</t>
+          <t>0,0; 8,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 12,27</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 13,71</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 7,89</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,66; 15,12</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,19</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,28; 11,35</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,23</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 12,17</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,32</t>
+          <t>0,0; 7,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 8,82</t>
+          <t>1,36; 8,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 9,15</t>
+          <t>1,6; 9,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,64</t>
+          <t>0,0; 7,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 8,76</t>
+          <t>0,57; 8,03</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5,99%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7,05%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,5%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5,49%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 11,61</t>
+          <t>0,73; 6,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 7,35</t>
+          <t>1,99; 9,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 9,77</t>
+          <t>2,22; 9,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,43</t>
+          <t>1,62; 20,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,15</t>
+          <t>3,26; 11,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 8,94</t>
+          <t>0,69; 6,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 10,27</t>
+          <t>2,85; 10,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 18,6</t>
+          <t>0,64; 5,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 7,68</t>
+          <t>2,79; 7,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,46</t>
+          <t>1,61; 6,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,51; 8,81</t>
+          <t>3,36; 8,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 10,14</t>
+          <t>1,49; 12,03</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>9,47%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>3,23%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>5,01%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 18,37</t>
+          <t>1,19; 11,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,56</t>
+          <t>1,93; 10,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 10,54</t>
+          <t>0,0; 5,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,61</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 10,55</t>
+          <t>3,96; 16,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 11,22</t>
+          <t>0,82; 8,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,57</t>
+          <t>1,75; 10,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,48</t>
+          <t>0,0; 6,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,71; 11,25</t>
+          <t>3,22; 10,82</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 7,56</t>
+          <t>2,23; 7,57</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 6,14</t>
+          <t>1,23; 6,43</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,47</t>
+          <t>0,38; 3,41</t>
         </is>
       </c>
     </row>
@@ -1349,44 +1349,44 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>11,48%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>5,17%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2,91%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>3,76%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11,48%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
           <t>8,15%</t>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,65; 13,97</t>
+          <t>5,5; 22,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,47</t>
+          <t>0,0; 8,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,03</t>
+          <t>0,0; 10,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>0,0; 9,21</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1,64; 12,7</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 13,72</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 13,56</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>4,05; 22,53</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,41</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 10,22</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,63</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,69; 13,85</t>
+          <t>4,28; 15,34</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,77</t>
+          <t>0,0; 7,31</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,9; 7,8</t>
+          <t>0,9; 7,85</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,66</t>
+          <t>0,0; 4,53</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>5,91%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>4,0%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>3,86%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,44</t>
+          <t>3,17; 6,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,87</t>
+          <t>2,59; 6,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,86</t>
+          <t>1,53; 4,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,84</t>
+          <t>1,9; 6,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,82</t>
+          <t>4,02; 8,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,93</t>
+          <t>2,53; 6,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,44</t>
+          <t>2,34; 6,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,74</t>
+          <t>1,18; 3,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,97; 6,84</t>
+          <t>4,13; 7,12</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,37</t>
+          <t>2,98; 5,42</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,47</t>
+          <t>2,22; 4,49</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,77</t>
+          <t>1,77; 4,74</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,62 +1859,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2244</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4761</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2218</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>3778</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1746</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2244</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1871</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3581</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6021</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5147</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3581</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6021</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>6632</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>629; 6466</t>
+          <t>0; 4986</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1370; 8054</t>
+          <t>718; 6038</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>0; 3598</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1651; 9823</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>632; 5991</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1373; 7835</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0; 5542</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4816</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>722; 5471</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0; 5934</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2356; 11787</t>
+          <t>0; 6399</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1366; 7995</t>
+          <t>1370; 7517</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2817; 10824</t>
+          <t>2821; 11733</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4061</t>
+          <t>0; 3585</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2856; 13473</t>
+          <t>2998; 13464</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2477</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2187</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1269</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2440</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2477</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>575</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3016</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>618; 5827</t>
+          <t>626; 5665</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4477</t>
+          <t>660; 5334</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>657; 6635</t>
+          <t>0; 3184</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>624; 5381</t>
+          <t>0; 3606</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>632; 6261</t>
+          <t>617; 5719</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>659; 5380</t>
+          <t>0; 3946</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2962</t>
+          <t>674; 6939</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3715</t>
+          <t>642; 6140</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2122; 9428</t>
+          <t>1984; 9022</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>671; 7203</t>
+          <t>1270; 7208</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>682; 8140</t>
+          <t>689; 7266</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1191; 7249</t>
+          <t>1002; 6587</t>
         </is>
       </c>
     </row>
@@ -2207,37 +2207,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2275,62 +2275,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2714</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>533</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2730</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2714</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3248</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3364</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>1399</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1507</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>3248</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>3364</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1399</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>1923</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2773</t>
+          <t>637; 6270</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>682; 6326</t>
+          <t>0; 3242</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>0; 4209</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4727</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2761</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>691; 6311</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2567</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>682; 6056</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3276</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4174</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4830</t>
+          <t>0; 2142</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1168; 7796</t>
+          <t>1204; 7491</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1316; 7459</t>
+          <t>1301; 7465</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4345</t>
+          <t>0; 4839</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>676; 5620</t>
+          <t>363; 5102</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2549</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4227</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5695</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7331</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>6923</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2283</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>6103</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2433</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2549</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4227</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5695</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7253</t>
+          <t>2381</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>9712</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3785; 11389</t>
+          <t>703; 6173</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>627; 6706</t>
+          <t>1946; 9252</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2971; 10853</t>
+          <t>2284; 10097</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>788; 7138</t>
+          <t>1980; 25226</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>636; 5916</t>
+          <t>3204; 11413</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1477; 8761</t>
+          <t>628; 5951</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2678; 10575</t>
+          <t>3168; 11842</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1814; 23695</t>
+          <t>696; 6312</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5690; 14928</t>
+          <t>5427; 15150</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3431; 12214</t>
+          <t>3040; 11426</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7518; 18855</t>
+          <t>7185; 18422</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3760; 24187</t>
+          <t>3452; 27823</t>
         </is>
       </c>
     </row>
@@ -2623,37 +2623,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2916</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4052</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>761</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>5177</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2653</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>3464</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1458</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2916</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>4052</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>2220</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2289; 10041</t>
+          <t>834; 7755</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>707; 6219</t>
+          <t>1425; 7607</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1036; 7292</t>
+          <t>0; 3939</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 5215</t>
+          <t>0; 2756</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>808; 7388</t>
+          <t>2163; 9250</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1400; 8264</t>
+          <t>674; 6649</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3366</t>
+          <t>1210; 7533</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3590</t>
+          <t>0; 4671</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4630; 14029</t>
+          <t>4012; 13490</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3431; 11782</t>
+          <t>3474; 11802</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1615; 8758</t>
+          <t>1756; 9172</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>665; 5964</t>
+          <t>618; 5560</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,44 +2899,44 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>2068</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>747</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1225</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>4102</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
           <t>6170</t>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>651</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>661; 5590</t>
+          <t>1965; 8139</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3718</t>
+          <t>0; 3176</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4249</t>
+          <t>0; 3341</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
+          <t>0; 4031</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>656; 5078</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3526</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4422</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1447; 8049</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0; 3531</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>0; 3291</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0; 4250</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2796; 10485</t>
+          <t>3241; 11619</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4909</t>
+          <t>0; 4618</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>586; 5055</t>
+          <t>581; 5087</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 3261</t>
+          <t>0; 4123</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>16121</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>13790</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>9713</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>15531</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>19106</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>13460</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>13233</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>8668</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>16121</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>13790</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>9713</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>16369</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>25037</t>
+          <t>24154</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12772; 27283</t>
+          <t>10822; 23267</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8483; 19770</t>
+          <t>8876; 20729</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7967; 20068</t>
+          <t>5330; 15083</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4663; 14854</t>
+          <t>8666; 31038</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10913; 23315</t>
+          <t>12987; 27393</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8791; 20349</t>
+          <t>8521; 20898</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4934; 15427</t>
+          <t>8024; 20658</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9043; 32267</t>
+          <t>4635; 15102</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>26408; 45472</t>
+          <t>27445; 47318</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18876; 36497</t>
+          <t>20238; 36843</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16062; 30873</t>
+          <t>15307; 30972</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>16414; 41248</t>
+          <t>15021; 40134</t>
         </is>
       </c>
     </row>
